--- a/data/trans_orig/P41A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>28431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>54624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28504</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>34064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31148</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57637</t>
+          <t>56628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>135215</t>
+          <t>136879</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>182163</t>
+          <t>180305</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104276</t>
+          <t>103335</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145415</t>
+          <t>146590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>251801</t>
+          <t>252675</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>312165</t>
+          <t>316287</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34636</t>
+          <t>36423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63699</t>
+          <t>65034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35015</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62345</t>
+          <t>62861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79003</t>
+          <t>76307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118391</t>
+          <t>114799</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>755138</t>
+          <t>754159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>810306</t>
+          <t>808298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1065292</t>
+          <t>1063552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1120700</t>
+          <t>1117144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1836522</t>
+          <t>1835721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1911204</t>
+          <t>1915028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40510</t>
+          <t>39020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57544</t>
+          <t>59892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55448</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89235</t>
+          <t>90772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28688</t>
+          <t>29854</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68035</t>
+          <t>67051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108067</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92143</t>
+          <t>91690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>135130</t>
+          <t>135279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185728</t>
+          <t>185064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>661833</t>
+          <t>666618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>741986</t>
+          <t>746055</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>491887</t>
+          <t>487233</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>566521</t>
+          <t>564234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1177802</t>
+          <t>1174064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1285444</t>
+          <t>1287286</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>180745</t>
+          <t>184003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>236511</t>
+          <t>237276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>181335</t>
+          <t>183784</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234968</t>
+          <t>234577</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>373804</t>
+          <t>375803</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457488</t>
+          <t>453095</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>619005</t>
+          <t>614040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>698986</t>
+          <t>692359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>675813</t>
+          <t>672732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>753091</t>
+          <t>755247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1319738</t>
+          <t>1318070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1433162</t>
+          <t>1429364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21024</t>
+          <t>22449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>23735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45372</t>
+          <t>45648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32401</t>
+          <t>33164</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58164</t>
+          <t>59719</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>196094</t>
+          <t>197438</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>244899</t>
+          <t>244297</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>150881</t>
+          <t>150772</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>193469</t>
+          <t>192865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>359098</t>
+          <t>358189</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>421548</t>
+          <t>420652</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>60451</t>
+          <t>59170</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92687</t>
+          <t>92768</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>72512</t>
+          <t>71771</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107162</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>141413</t>
+          <t>138497</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>189719</t>
+          <t>184845</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>178615</t>
+          <t>176943</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>223444</t>
+          <t>223716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>170271</t>
+          <t>169831</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>213269</t>
+          <t>211118</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>359962</t>
+          <t>361312</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>420478</t>
+          <t>421517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>78068</t>
+          <t>80588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>54272</t>
+          <t>54459</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>86106</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>109304</t>
+          <t>109388</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>153895</t>
+          <t>155236</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11569</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>29296</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>22730</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>46591</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>115641</t>
+          <t>114920</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>161212</t>
+          <t>163785</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>89168</t>
+          <t>89198</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>129160</t>
+          <t>130551</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>214869</t>
+          <t>213439</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>280417</t>
+          <t>275878</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1019627</t>
+          <t>1024901</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1134166</t>
+          <t>1136736</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>769448</t>
+          <t>773814</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>875465</t>
+          <t>877107</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1833258</t>
+          <t>1829137</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1972358</t>
+          <t>1979009</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>297121</t>
+          <t>294785</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>368825</t>
+          <t>364899</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>305640</t>
+          <t>310255</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>378717</t>
+          <t>377665</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>630231</t>
+          <t>623981</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>730984</t>
+          <t>723018</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1579124</t>
+          <t>1582667</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1695955</t>
+          <t>1694962</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1939284</t>
+          <t>1941571</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2055678</t>
+          <t>2058196</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3547393</t>
+          <t>3554265</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3718224</t>
+          <t>3725739</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>21255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30292</t>
+          <t>29732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55720</t>
+          <t>55097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42879</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73447</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80304</t>
+          <t>79531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119514</t>
+          <t>120655</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104275</t>
+          <t>103842</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147481</t>
+          <t>146459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73594</t>
+          <t>73518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111519</t>
+          <t>111816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187319</t>
+          <t>188253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>245592</t>
+          <t>245070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29154</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>54528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43863</t>
+          <t>42889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72937</t>
+          <t>74325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79567</t>
+          <t>78528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118642</t>
+          <t>118765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>728453</t>
+          <t>727565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>781242</t>
+          <t>778169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1083273</t>
+          <t>1084248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1137871</t>
+          <t>1138278</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1826210</t>
+          <t>1824195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1903692</t>
+          <t>1906448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47492</t>
+          <t>48246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25278</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49341</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>54524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89429</t>
+          <t>88383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>18319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40174</t>
+          <t>40683</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54695</t>
+          <t>53444</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>122521</t>
+          <t>122799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173551</t>
+          <t>172002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132942</t>
+          <t>133133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>182346</t>
+          <t>184298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267041</t>
+          <t>264802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337160</t>
+          <t>334789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>685709</t>
+          <t>690803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>775307</t>
+          <t>779202</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>360164</t>
+          <t>359078</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>429632</t>
+          <t>429405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1067460</t>
+          <t>1067940</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1180963</t>
+          <t>1189150</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>187960</t>
+          <t>185565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>243226</t>
+          <t>245809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>230107</t>
+          <t>227002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>292301</t>
+          <t>291601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>430356</t>
+          <t>429700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>511923</t>
+          <t>517574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>781289</t>
+          <t>776635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>872338</t>
+          <t>869275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>844219</t>
+          <t>841282</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>929430</t>
+          <t>931748</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1653836</t>
+          <t>1648801</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1773037</t>
+          <t>1779254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25263</t>
+          <t>23703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>25238</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25719</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>51129</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50308</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83714</t>
+          <t>83899</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>190947</t>
+          <t>190716</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>237540</t>
+          <t>235555</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>140188</t>
+          <t>136925</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>182786</t>
+          <t>181258</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>341425</t>
+          <t>341275</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>405702</t>
+          <t>407172</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49200</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>81863</t>
+          <t>83900</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60024</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>92181</t>
+          <t>93565</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120430</t>
+          <t>119716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>165975</t>
+          <t>166668</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>131019</t>
+          <t>130909</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>174839</t>
+          <t>174836</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>157903</t>
+          <t>159454</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>202187</t>
+          <t>200846</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>302245</t>
+          <t>302084</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>363148</t>
+          <t>362902</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -8111,12 +8111,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>34559</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>65992</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>42194</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>75650</t>
+          <t>72868</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>84435</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>130122</t>
+          <t>127691</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -8337,12 +8337,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>28800</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>55388</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>46891</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>79772</t>
+          <t>78779</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -8563,12 +8563,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>196043</t>
+          <t>197323</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>257492</t>
+          <t>258086</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>209656</t>
+          <t>209320</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>275405</t>
+          <t>272909</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>421540</t>
+          <t>426339</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>505687</t>
+          <t>510034</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1010716</t>
+          <t>1014607</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1123148</t>
+          <t>1126565</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>595476</t>
+          <t>601612</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>687902</t>
+          <t>696037</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1643058</t>
+          <t>1642161</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1789676</t>
+          <t>1789501</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>287135</t>
+          <t>287860</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>359008</t>
+          <t>358395</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>350615</t>
+          <t>350202</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>430088</t>
+          <t>430479</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>660286</t>
+          <t>662691</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>761437</t>
+          <t>765637</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -8902,12 +8902,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1674347</t>
+          <t>1667592</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1792469</t>
+          <t>1793022</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2120607</t>
+          <t>2115240</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2237579</t>
+          <t>2238014</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3832161</t>
+          <t>3829004</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3999978</t>
+          <t>3995702</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -9363,12 +9363,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>17479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29178</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>19077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39481</t>
+          <t>40442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -9928,12 +9928,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>68841</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>104601</t>
+          <t>103818</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50660</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79623</t>
+          <t>79973</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>127061</t>
+          <t>122961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>174994</t>
+          <t>171692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>40851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68199</t>
+          <t>69424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10076,12 +10076,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47065</t>
+          <t>45723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69427</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108023</t>
+          <t>108010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>569004</t>
+          <t>567942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613249</t>
+          <t>613258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>854472</t>
+          <t>852871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>893637</t>
+          <t>892075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1433175</t>
+          <t>1433258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1494862</t>
+          <t>1497694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -10384,12 +10384,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42638</t>
+          <t>43663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10399,12 +10399,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>45152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>79791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -10836,12 +10836,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>55610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>88706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74850</t>
+          <t>74971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113204</t>
+          <t>113070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138396</t>
+          <t>139224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190654</t>
+          <t>191750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -10949,12 +10949,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>611869</t>
+          <t>610414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>698007</t>
+          <t>691848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>400703</t>
+          <t>399095</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>472494</t>
+          <t>470937</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1036480</t>
+          <t>1032732</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1147412</t>
+          <t>1148382</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11034,12 +11034,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -11062,12 +11062,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>281968</t>
+          <t>281716</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>349378</t>
+          <t>347761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>333592</t>
+          <t>338265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>401261</t>
+          <t>405317</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11112,47 +11112,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>683803</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>636342</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>732121</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>16,89%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>20,31%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>683803</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>635969</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>730208</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>956323</t>
+          <t>959347</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1050038</t>
+          <t>1044800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11210,12 +11210,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>997689</t>
+          <t>999105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1088748</t>
+          <t>1089003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1980796</t>
+          <t>1982843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2105472</t>
+          <t>2112998</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -11405,12 +11405,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11440,12 +11440,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -11857,12 +11857,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32685</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11892,12 +11892,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43233</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67016</t>
+          <t>66958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -11970,12 +11970,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>174694</t>
+          <t>173584</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>221603</t>
+          <t>219392</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11985,12 +11985,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12005,12 +12005,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>136032</t>
+          <t>136025</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>177531</t>
+          <t>177378</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>323277</t>
+          <t>323847</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>386282</t>
+          <t>387364</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12055,12 +12055,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -12083,12 +12083,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>77462</t>
+          <t>76950</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>114447</t>
+          <t>113383</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>97907</t>
+          <t>101136</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>137851</t>
+          <t>137951</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12153,12 +12153,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>187930</t>
+          <t>184457</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>240865</t>
+          <t>239291</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12168,12 +12168,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -12196,12 +12196,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>202030</t>
+          <t>202805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>251055</t>
+          <t>250685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>211472</t>
+          <t>209961</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>257457</t>
+          <t>257463</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>425583</t>
+          <t>428287</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>493748</t>
+          <t>493273</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12281,12 +12281,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -12426,12 +12426,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>60176</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12441,12 +12441,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12461,12 +12461,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37256</t>
+          <t>37247</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>65138</t>
+          <t>65006</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77996</t>
+          <t>76577</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>116776</t>
+          <t>114386</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -12687,12 +12687,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -12878,12 +12878,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>87044</t>
+          <t>86693</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>127091</t>
+          <t>129702</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12913,12 +12913,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>113462</t>
+          <t>114429</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>157772</t>
+          <t>161436</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12928,12 +12928,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>212211</t>
+          <t>211139</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>272040</t>
+          <t>271699</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>876702</t>
+          <t>883409</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>983826</t>
+          <t>993176</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>614647</t>
+          <t>610081</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>701371</t>
+          <t>700331</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1519086</t>
+          <t>1523412</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1665551</t>
+          <t>1661863</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -13104,12 +13104,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>416813</t>
+          <t>423644</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>504161</t>
+          <t>503274</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>478452</t>
+          <t>484003</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>565240</t>
+          <t>564752</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>919984</t>
+          <t>927405</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1039666</t>
+          <t>1038839</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -13217,12 +13217,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1759947</t>
+          <t>1759990</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1883282</t>
+          <t>1880199</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2092859</t>
+          <t>2094110</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2205669</t>
+          <t>2206066</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13267,12 +13267,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3889215</t>
+          <t>3889385</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4063493</t>
+          <t>4055698</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -13673,32 +13673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13708,32 +13708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13743,32 +13743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -13786,32 +13786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>111639</t>
+          <t>133805</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94968</t>
+          <t>113671</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130901</t>
+          <t>154985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13821,32 +13821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>238091</t>
+          <t>264551</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219682</t>
+          <t>244239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258395</t>
+          <t>285661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13856,32 +13856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>349730</t>
+          <t>398356</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>324510</t>
+          <t>371515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>376454</t>
+          <t>428526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -13899,102 +13899,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7135</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>7904</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>16117</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3035</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1177</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6771</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>7733</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>3726</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>16691</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -14125,32 +14125,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>11251</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17826</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14160,67 +14160,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>17532</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>10395</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>25907</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>15363</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>9253</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>25609</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -14238,32 +14238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36306</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54104</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14273,32 +14273,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27280</t>
+          <t>31153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14308,32 +14308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>54426</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39368</t>
+          <t>42802</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72905</t>
+          <t>73814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -14351,32 +14351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28514</t>
+          <t>33530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14386,32 +14386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14421,32 +14421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38757</t>
+          <t>45562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -14464,32 +14464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>311375</t>
+          <t>341365</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288553</t>
+          <t>318900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330652</t>
+          <t>363637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14499,32 +14499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>424385</t>
+          <t>462958</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>404443</t>
+          <t>439005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444079</t>
+          <t>484156</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14534,32 +14534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>735759</t>
+          <t>804323</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707691</t>
+          <t>774262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>763518</t>
+          <t>835576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -14577,17 +14577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>492536</t>
+          <t>551808</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492536</t>
+          <t>551808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>492536</t>
+          <t>551808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14612,17 +14612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>701387</t>
+          <t>771656</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>701387</t>
+          <t>771656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>701387</t>
+          <t>771656</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14647,17 +14647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1193922</t>
+          <t>1323464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1193922</t>
+          <t>1323464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1193922</t>
+          <t>1323464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14694,32 +14694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>28145</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42619</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14729,32 +14729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14764,32 +14764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>36047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64912</t>
+          <t>64989</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -14807,32 +14807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>474285</t>
+          <t>513574</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>332838</t>
+          <t>460212</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>560713</t>
+          <t>565007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14842,32 +14842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>527798</t>
+          <t>535240</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>396612</t>
+          <t>493956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>676864</t>
+          <t>573443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14877,32 +14877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1002083</t>
+          <t>1048813</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>810587</t>
+          <t>993349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1185753</t>
+          <t>1118450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -14920,32 +14920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14955,32 +14955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32648</t>
+          <t>35092</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14990,32 +14990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>37815</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>25581</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55783</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -15146,32 +15146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63804</t>
+          <t>76469</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84673</t>
+          <t>97786</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15181,32 +15181,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>74048</t>
+          <t>83235</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53570</t>
+          <t>68949</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91915</t>
+          <t>101081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15216,32 +15216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>137852</t>
+          <t>159704</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105919</t>
+          <t>137883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165994</t>
+          <t>184459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -15259,32 +15259,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>413899</t>
+          <t>450760</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>268201</t>
+          <t>410015</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>482525</t>
+          <t>495515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15294,32 +15294,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>260258</t>
+          <t>291581</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>180688</t>
+          <t>262022</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>309073</t>
+          <t>324401</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15329,32 +15329,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>674157</t>
+          <t>742340</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>518408</t>
+          <t>690735</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>767399</t>
+          <t>798463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -15372,32 +15372,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>125013</t>
+          <t>139620</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85067</t>
+          <t>114854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156912</t>
+          <t>168951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15407,32 +15407,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>141647</t>
+          <t>162909</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101234</t>
+          <t>142893</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171580</t>
+          <t>189574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15442,32 +15442,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>266659</t>
+          <t>302529</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>206540</t>
+          <t>271446</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>311110</t>
+          <t>337160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -15485,32 +15485,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1001938</t>
+          <t>825441</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>836268</t>
+          <t>775075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1349682</t>
+          <t>876532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15520,32 +15520,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>999522</t>
+          <t>871989</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>858788</t>
+          <t>829908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1279101</t>
+          <t>909282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15555,32 +15555,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2001459</t>
+          <t>1697430</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1748556</t>
+          <t>1632133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2523451</t>
+          <t>1758903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -15598,17 +15598,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2124225</t>
+          <t>2053902</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2124225</t>
+          <t>2053902</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2124225</t>
+          <t>2053902</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15633,17 +15633,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2043412</t>
+          <t>1988731</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2043412</t>
+          <t>1988731</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2043412</t>
+          <t>1988731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15668,17 +15668,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4167637</t>
+          <t>4042633</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4167637</t>
+          <t>4042633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4167637</t>
+          <t>4042633</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15715,32 +15715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15750,32 +15750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15785,32 +15785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>9886</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -15828,32 +15828,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>112712</t>
+          <t>126531</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93942</t>
+          <t>105193</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137732</t>
+          <t>151316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15863,32 +15863,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>128987</t>
+          <t>145554</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110872</t>
+          <t>127345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149718</t>
+          <t>165999</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15898,32 +15898,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>241698</t>
+          <t>272085</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>214301</t>
+          <t>243684</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272183</t>
+          <t>305547</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -15941,32 +15941,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15976,32 +15976,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26070</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16011,32 +16011,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36014</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -16134,12 +16134,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -16167,32 +16167,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>35417</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>26876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48633</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16202,32 +16202,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28160</t>
+          <t>32758</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37643</t>
+          <t>43756</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16237,32 +16237,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>63578</t>
+          <t>70392</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50540</t>
+          <t>56441</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>78688</t>
+          <t>86693</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -16280,32 +16280,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>131356</t>
+          <t>145844</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>110365</t>
+          <t>122135</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>154172</t>
+          <t>171829</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16315,32 +16315,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>95288</t>
+          <t>104360</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>87682</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>112200</t>
+          <t>121858</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16350,32 +16350,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>226644</t>
+          <t>250205</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>198723</t>
+          <t>223075</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>256042</t>
+          <t>279483</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -16393,32 +16393,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>62674</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16428,32 +16428,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>75977</t>
+          <t>88507</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60901</t>
+          <t>73736</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>91157</t>
+          <t>106794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16463,32 +16463,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>117727</t>
+          <t>132602</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>97580</t>
+          <t>111855</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>139795</t>
+          <t>156475</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -16506,32 +16506,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>262846</t>
+          <t>290158</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>234855</t>
+          <t>263661</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>289930</t>
+          <t>316026</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16541,32 +16541,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>274668</t>
+          <t>302086</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>251878</t>
+          <t>279867</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>296214</t>
+          <t>324502</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16576,32 +16576,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>537513</t>
+          <t>592244</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>503841</t>
+          <t>561230</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>577518</t>
+          <t>633579</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -16619,17 +16619,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>601591</t>
+          <t>664661</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>601591</t>
+          <t>664661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>601591</t>
+          <t>664661</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16654,17 +16654,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>623871</t>
+          <t>695229</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>623871</t>
+          <t>695229</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>623871</t>
+          <t>695229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16689,17 +16689,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1225462</t>
+          <t>1359891</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1225462</t>
+          <t>1359891</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1225462</t>
+          <t>1359891</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16736,32 +16736,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>24768</t>
+          <t>26421</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>55127</t>
+          <t>56990</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16771,17 +16771,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34069</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16791,12 +16791,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16806,32 +16806,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>64816</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>47725</t>
+          <t>49928</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>80097</t>
+          <t>84128</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -16849,32 +16849,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>698636</t>
+          <t>773910</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>533178</t>
+          <t>722069</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>781106</t>
+          <t>837274</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16884,32 +16884,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>894876</t>
+          <t>945345</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>740006</t>
+          <t>893805</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1051569</t>
+          <t>991868</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1593512</t>
+          <t>1719255</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1373033</t>
+          <t>1646296</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1775119</t>
+          <t>1803883</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -16962,32 +16962,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>20388</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -16997,32 +16997,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>44778</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17032,32 +17032,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>71883</t>
+          <t>81344</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>54331</t>
+          <t>64242</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>89916</t>
+          <t>100082</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -17075,7 +17075,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -17170,7 +17170,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -17188,32 +17188,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>109068</t>
+          <t>125354</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>79727</t>
+          <t>105383</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>131975</t>
+          <t>149640</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17223,32 +17223,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>107725</t>
+          <t>122274</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>83568</t>
+          <t>107031</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>126377</t>
+          <t>142947</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17258,32 +17258,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>216792</t>
+          <t>247628</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>181052</t>
+          <t>218744</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>249788</t>
+          <t>279499</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -17301,32 +17301,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>581561</t>
+          <t>632586</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>445853</t>
+          <t>582127</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>656614</t>
+          <t>688036</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17336,32 +17336,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>373665</t>
+          <t>417004</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>301398</t>
+          <t>382825</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>419915</t>
+          <t>451534</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17371,32 +17371,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>955226</t>
+          <t>1049589</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>813460</t>
+          <t>988309</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1042977</t>
+          <t>1119479</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -17414,32 +17414,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>181929</t>
+          <t>203110</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>139217</t>
+          <t>173462</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>217845</t>
+          <t>240922</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17449,32 +17449,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>228112</t>
+          <t>263203</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>180341</t>
+          <t>234124</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>261095</t>
+          <t>293427</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17484,32 +17484,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>410041</t>
+          <t>466313</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>341811</t>
+          <t>422985</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>453769</t>
+          <t>515751</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -17527,32 +17527,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1576158</t>
+          <t>1456964</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1419095</t>
+          <t>1388243</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2032278</t>
+          <t>1513040</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17562,32 +17562,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1698574</t>
+          <t>1637033</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1557040</t>
+          <t>1587416</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2033850</t>
+          <t>1689703</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17597,32 +17597,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3274732</t>
+          <t>3093998</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3047954</t>
+          <t>3015066</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3872699</t>
+          <t>3172290</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -17640,17 +17640,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3218352</t>
+          <t>3270371</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3218352</t>
+          <t>3270371</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3218352</t>
+          <t>3270371</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17675,17 +17675,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3368670</t>
+          <t>3455616</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3368670</t>
+          <t>3455616</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3368670</t>
+          <t>3455616</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17710,17 +17710,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>6587022</t>
+          <t>6725988</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>6587022</t>
+          <t>6725988</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6587022</t>
+          <t>6725988</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
